--- a/output/pdf_financials_xlsx/PHOS.xlsx
+++ b/output/pdf_financials_xlsx/PHOS.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/PHOS.xlsx
+++ b/output/pdf_financials_xlsx/PHOS.xlsx
@@ -429,12 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,6 +461,11 @@
           <t>2025-02</t>
         </is>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -480,6 +486,9 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -493,6 +502,9 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -506,6 +518,9 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -519,6 +534,9 @@
       <c r="C7" s="3" t="n">
         <v>0.066967</v>
       </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -530,7 +548,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>0.47127</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.998342</v>
       </c>
     </row>
     <row r="9">
@@ -543,7 +564,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.677826</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.597826</v>
       </c>
     </row>
     <row r="10">
@@ -558,6 +582,9 @@
       <c r="C10" s="3" t="n">
         <v>0.47127</v>
       </c>
+      <c r="D10" s="3" t="n">
+        <v>1.596168</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -571,6 +598,9 @@
       <c r="C11" s="3" t="n">
         <v>-0.47127</v>
       </c>
+      <c r="D11" s="3" t="n">
+        <v>-1.596168</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -584,6 +614,9 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -592,10 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -610,6 +646,9 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -623,6 +662,9 @@
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -636,6 +678,9 @@
       <c r="C16" s="3" t="n">
         <v>-7.627414</v>
       </c>
+      <c r="D16" s="3" t="n">
+        <v>-23.442719</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -644,10 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -666,6 +714,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -683,6 +736,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -696,6 +754,9 @@
       <c r="C20" s="3" t="n">
         <v>-7.627414</v>
       </c>
+      <c r="D20" s="3" t="n">
+        <v>-23.442719</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -709,6 +770,9 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -722,6 +786,9 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -735,6 +802,9 @@
       <c r="C23" s="3" t="n">
         <v>-7.627414</v>
       </c>
+      <c r="D23" s="3" t="n">
+        <v>-23.442719</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -748,6 +818,9 @@
       <c r="C24" s="3" t="n">
         <v>-0.1</v>
       </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.21</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -761,6 +834,9 @@
       <c r="C25" s="3" t="n">
         <v>-0.1</v>
       </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.21</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -774,6 +850,9 @@
       <c r="C26" s="3" t="n">
         <v>76.27414</v>
       </c>
+      <c r="D26" s="3" t="n">
+        <v>111.631995</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -787,6 +866,9 @@
       <c r="C27" s="3" t="n">
         <v>-7.627414</v>
       </c>
+      <c r="D27" s="3" t="n">
+        <v>-23.442719</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -800,6 +882,9 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D28" s="3" t="n">
+        <v>0.013477</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -813,6 +898,9 @@
       <c r="C29" s="3" t="n">
         <v>-7.627414</v>
       </c>
+      <c r="D29" s="3" t="n">
+        <v>-23.429242</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -830,6 +918,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -843,6 +936,9 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -860,6 +956,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -880,6 +981,9 @@
       <c r="C34" s="3" t="n">
         <v>1.87355</v>
       </c>
+      <c r="D34" s="3" t="n">
+        <v>20.190457</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -893,6 +997,9 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -906,6 +1013,9 @@
       <c r="C36" s="3" t="n">
         <v>1.87355</v>
       </c>
+      <c r="D36" s="3" t="n">
+        <v>20.190457</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -919,6 +1029,9 @@
       <c r="C37" s="3" t="n">
         <v>0.047336</v>
       </c>
+      <c r="D37" s="3" t="n">
+        <v>0.101042</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -932,6 +1045,9 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -945,6 +1061,9 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -958,6 +1077,9 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -971,6 +1093,9 @@
       <c r="C41" s="3" t="n">
         <v>0.047336</v>
       </c>
+      <c r="D41" s="3" t="n">
+        <v>0.101042</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -984,6 +1109,9 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -997,6 +1125,9 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1010,6 +1141,9 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1023,6 +1157,9 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1036,6 +1173,9 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1049,6 +1189,9 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1062,6 +1205,9 @@
       <c r="C48" s="3" t="n">
         <v>1.771978</v>
       </c>
+      <c r="D48" s="3" t="n">
+        <v>4.481777</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1075,6 +1221,9 @@
       <c r="C49" s="3" t="n">
         <v>3.692864</v>
       </c>
+      <c r="D49" s="3" t="n">
+        <v>24.773276</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1088,6 +1237,9 @@
       <c r="C50" s="3" t="n">
         <v>0.168174</v>
       </c>
+      <c r="D50" s="3" t="n">
+        <v>0.16996</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1101,6 +1253,9 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1114,6 +1269,9 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1127,6 +1285,9 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1140,6 +1301,9 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1157,6 +1321,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1170,6 +1339,9 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1183,6 +1355,9 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1196,6 +1371,9 @@
       <c r="C58" s="3" t="n">
         <v>3.591734</v>
       </c>
+      <c r="D58" s="3" t="n">
+        <v>3.711874</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1209,6 +1387,9 @@
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1222,6 +1403,9 @@
       <c r="C60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1235,6 +1419,9 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1248,6 +1435,9 @@
       <c r="C62" s="3" t="n">
         <v>3.759908</v>
       </c>
+      <c r="D62" s="3" t="n">
+        <v>3.881834</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1261,6 +1451,9 @@
       <c r="C63" s="3" t="n">
         <v>7.452772</v>
       </c>
+      <c r="D63" s="3" t="n">
+        <v>28.65511</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1274,6 +1467,9 @@
       <c r="C64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1287,6 +1483,9 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1300,6 +1499,9 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1313,6 +1515,9 @@
       <c r="C67" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1326,6 +1531,9 @@
       <c r="C68" s="3" t="n">
         <v>0.342964</v>
       </c>
+      <c r="D68" s="3" t="n">
+        <v>2.883651</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1339,6 +1547,9 @@
       <c r="C69" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1352,6 +1563,9 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1365,6 +1579,9 @@
       <c r="C71" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1378,6 +1595,9 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1391,6 +1611,9 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1404,6 +1627,9 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1415,7 +1641,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0</v>
+        <v>0.718477</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.221678</v>
       </c>
     </row>
     <row r="76">
@@ -1429,10 +1658,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C76" s="3" t="n">
+        <v>1.061441</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>3.105329</v>
       </c>
     </row>
     <row r="77">
@@ -1447,6 +1677,9 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1460,6 +1693,9 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D78" s="3" t="n">
+        <v>0.060451</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1473,6 +1709,9 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D79" s="3" t="n">
+        <v>0.060451</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1490,6 +1729,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D80" s="3" t="n">
+        <v>0.002441170875217365</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1503,6 +1745,9 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1516,6 +1761,9 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1529,6 +1777,9 @@
       <c r="C83" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1542,6 +1793,9 @@
       <c r="C84" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1555,6 +1809,9 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D85" s="3" t="n">
+        <v>0.726213</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1567,10 +1824,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0.786664</v>
       </c>
     </row>
     <row r="87">
@@ -1585,6 +1843,9 @@
       <c r="C87" s="3" t="n">
         <v>1.061441</v>
       </c>
+      <c r="D87" s="3" t="n">
+        <v>3.891993</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -1598,6 +1859,9 @@
       <c r="C88" s="3" t="n">
         <v>30.657018</v>
       </c>
+      <c r="D88" s="3" t="n">
+        <v>72.80600800000001</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -1611,6 +1875,9 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1624,6 +1891,9 @@
       <c r="C90" s="3" t="n">
         <v>-29.575088</v>
       </c>
+      <c r="D90" s="3" t="n">
+        <v>-53.017807</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1637,6 +1907,9 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -1650,6 +1923,9 @@
       <c r="C92" s="3" t="n">
         <v>5.309401</v>
       </c>
+      <c r="D92" s="3" t="n">
+        <v>4.87479</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -1663,6 +1939,9 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -1676,6 +1955,9 @@
       <c r="C94" s="3" t="n">
         <v>6.391331</v>
       </c>
+      <c r="D94" s="3" t="n">
+        <v>24.763117</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -1689,6 +1971,9 @@
       <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1702,6 +1987,9 @@
       <c r="C96" s="3" t="n">
         <v>6.391331</v>
       </c>
+      <c r="D96" s="3" t="n">
+        <v>24.763117</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -1715,6 +2003,9 @@
       <c r="C97" s="3" t="n">
         <v>0.8575776905559435</v>
       </c>
+      <c r="D97" s="3" t="n">
+        <v>0.864178047126673</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1735,6 +2026,9 @@
       <c r="C99" s="3" t="n">
         <v>-7.627414</v>
       </c>
+      <c r="D99" s="3" t="n">
+        <v>-23.442719</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -1748,6 +2042,9 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1761,6 +2058,9 @@
       <c r="C101" s="3" t="n">
         <v>0.593351</v>
       </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.101042</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -1774,6 +2074,9 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -1787,6 +2090,9 @@
       <c r="C103" s="3" t="n">
         <v>0.251993</v>
       </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.934148</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -1798,7 +2104,10 @@
         <v>3.249711</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>-2.168118</v>
+        <v>-2.146868</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>2.540687</v>
       </c>
     </row>
     <row r="105">
@@ -1813,6 +2122,9 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -1824,7 +2136,10 @@
         <v>3.188052</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-1.322774</v>
+        <v>-1.301524</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1.505497</v>
       </c>
     </row>
     <row r="107">
@@ -1839,6 +2154,9 @@
       <c r="C107" s="3" t="n">
         <v>2.496911</v>
       </c>
+      <c r="D107" s="3" t="n">
+        <v>3.318721</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -1852,6 +2170,9 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -1865,6 +2186,9 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -1878,6 +2202,9 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -1891,6 +2218,9 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -1904,6 +2234,9 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -1917,6 +2250,9 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -1930,6 +2266,9 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -1943,6 +2282,9 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -1956,6 +2298,9 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -1969,6 +2314,9 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -1980,6 +2328,9 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1995,6 +2346,9 @@
       <c r="C119" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D119" s="3" t="n">
+        <v>-0.026743</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2008,6 +2362,9 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D120" s="3" t="n">
+        <v>1.119999</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2021,6 +2378,9 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2034,6 +2394,9 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2047,6 +2410,9 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2060,6 +2426,9 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2073,6 +2442,9 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2086,6 +2458,9 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2103,6 +2478,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2116,6 +2496,9 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D128" s="3" t="n">
+        <v>-0.1367</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -2129,6 +2512,9 @@
       <c r="C129" s="3" t="n">
         <v>2.695459</v>
       </c>
+      <c r="D129" s="3" t="n">
+        <v>39.583511</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -2142,6 +2528,9 @@
       <c r="C130" s="3" t="n">
         <v>7.496238</v>
       </c>
+      <c r="D130" s="3" t="n">
+        <v>1.87355</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -2155,6 +2544,9 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -2168,6 +2560,9 @@
       <c r="C132" s="3" t="n">
         <v>-5.622688</v>
       </c>
+      <c r="D132" s="3" t="n">
+        <v>18.316907</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -2181,6 +2576,9 @@
       <c r="C133" s="3" t="n">
         <v>1.87355</v>
       </c>
+      <c r="D133" s="3" t="n">
+        <v>20.190457</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -2194,6 +2592,9 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -2206,6 +2607,9 @@
       </c>
       <c r="C135" s="3" t="n">
         <v>-8.318147</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-21.239861</v>
       </c>
     </row>
   </sheetData>
@@ -2219,7 +2623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2259,6 +2663,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2266,18 +2675,31 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>February 28, 2025 February</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="5" t="n">
-        <v>0.002024</v>
+          <t>Cash and cash equivalents (note 5)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>1.87355</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>20.190457</v>
       </c>
     </row>
     <row r="3">
@@ -2293,19 +2715,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents (Note 5)</t>
+          <t>Restricted cash (note 5)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>7.496238</v>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.87355</v>
+        <v>0.035</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="4">
@@ -2321,19 +2748,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted cash (Note 5)</t>
+          <t>Amounts receivable</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RestrictedCash</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.025</v>
+        <v>0.640687</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.035</v>
+        <v>0.047336</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.101042</v>
       </c>
     </row>
     <row r="5">
@@ -2349,19 +2779,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prepaid expenses (Note 6)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.411438</v>
+          <t>Tax credits/grants receivable (note 21)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.159445</v>
+        <v>1.292291</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.348184</v>
       </c>
     </row>
     <row r="6">
@@ -2377,17 +2808,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tax credits recoverable (Note 9)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Prepaid expenses (note 6)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.244955</v>
+        <v>0.159445</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.093593</v>
       </c>
     </row>
     <row r="7">
@@ -2403,16 +2841,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prepaid financing expense (Note 8)</t>
+          <t>Prepaid financing expense (note 9)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" s="5" t="n">
-        <v>0.399095</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.332578</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2427,19 +2872,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Current Assets total</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AccountsReceivable</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.640687</v>
+        <v>8.972458</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.047336</v>
+        <v>3.692864</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>24.773276</v>
       </c>
     </row>
     <row r="9">
@@ -2450,24 +2898,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Non-Current Assets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Current Assets total</t>
+          <t>Investments (note 7)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>8.972458</v>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>3.692864</v>
+        <v>0.168174</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.16996</v>
       </c>
     </row>
     <row r="10">
@@ -2483,19 +2936,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Investments (Note 7)</t>
+          <t>Exploration and evaluation assets (note 8)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>InvestmentsAndAdvances</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0.132988</v>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.168174</v>
+        <v>3.591734</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.591734</v>
       </c>
     </row>
     <row r="11">
@@ -2511,17 +2969,26 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prepaid financing expense (Note 8)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
-        <v>0.332578</v>
+          <t>Right-of-use assets (note 10)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.12014</v>
       </c>
     </row>
     <row r="12">
@@ -2537,19 +3004,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets (Note 9)</t>
+          <t>Non-Current Assets total</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NetPPE</t>
+          <t>TotalNonCurrentAssets</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3.557734</v>
+        <v>4.0233</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3.591734</v>
+        <v>3.759908</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3.881834</v>
       </c>
     </row>
     <row r="13">
@@ -2565,19 +3035,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Non-Current Assets total</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TotalNonCurrentAssets</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>4.0233</v>
+        <v>12.995758</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3.759908</v>
+        <v>7.452772</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>28.65511</v>
       </c>
     </row>
     <row r="14">
@@ -2588,24 +3061,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Non-Current Assets</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total Assets</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>12.995758</v>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7.452772</v>
+        <v>0.342964</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.883651</v>
       </c>
     </row>
     <row r="15">
@@ -2621,19 +3099,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 18)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>2.532332</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.342964</v>
+          <t>Lease liabilities (note 11)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.038878</v>
       </c>
     </row>
     <row r="16">
@@ -2649,16 +3130,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability (Note 10)</t>
+          <t>Flow-through share premium liability (note 12)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" s="5" t="n">
-        <v>1.151052</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F16" s="5" t="n">
         <v>0.718477</v>
       </c>
+      <c r="G16" s="5" t="n">
+        <v>0.1828</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2673,20 +3159,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
+          <t>Current Liabilities total</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>3.683384</v>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" s="5" t="n">
         <v>1.061441</v>
       </c>
+      <c r="G17" s="5" t="n">
+        <v>3.105329</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2696,24 +3187,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Non-current Liabilities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Capital stock (Note 11)</t>
+          <t>Lease liabilities (note 11)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>26.342634</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>30.657018</v>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.060451</v>
       </c>
     </row>
     <row r="19">
@@ -2724,24 +3222,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Non-current Liabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contributed surplus (Note 11)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>4.917414</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>5.309401</v>
+          <t>Bridge loan (note 13)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.726213</v>
       </c>
     </row>
     <row r="20">
@@ -2752,24 +3253,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Non-current Liabilities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Non-current Liabilities total</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-21.947674</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-29.575088</v>
+          <t>TotalNonCurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.786664</v>
       </c>
     </row>
     <row r="21">
@@ -2780,24 +3288,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Non-current Liabilities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity</t>
+          <t>Total Liabilities</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>9.312374</v>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>6.391331</v>
+        <v>1.061441</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>3.891993</v>
       </c>
     </row>
     <row r="22">
@@ -2813,19 +3326,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders’ Equity</t>
+          <t>Capital stock (note 14)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>12.995758</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>7.452772</v>
+        <v>30.657018</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>72.80600800000001</v>
       </c>
     </row>
     <row r="23">
@@ -2836,147 +3354,177 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Subsequent events</t>
+          <t>Shares to be issued)                                           100,126</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Approved and authorized by the Board of Directors on June</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
-        <v>0.002025</v>
+          <t>Contributed surplus (note 14)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2.7e-05</v>
+        <v>5.309401</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>4.87479</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Shares to be issued)                                           100,126</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>-8.292468</v>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-7.627414</v>
+        <v>-29.575088</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-53.017807</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Non-cash expense</t>
+          <t>Shares to be issued)                                           100,126</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Share based compensation</t>
+          <t>Total Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1.646973</v>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2.496911</v>
+        <v>6.391331</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>24.763117</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Non-cash expense</t>
+          <t>Shares to be issued)                                           100,126</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financing fee</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>0.066515</v>
+          <t>Total Liabilities and Shareholders’ Equity</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.399095</v>
+        <v>7.452772</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>28.65511</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Non-cash expense</t>
+          <t>Subsequent events</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gain on amortization of flow-through share</t>
+          <t>Approved and authorized by the Board of Directors on June</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>-0.383219</v>
+        <v>0.002025</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-1.177421</v>
+        <v>0.002026</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>premium liability</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties</t>
+          <t>February 28, 2025 February</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.109325</v>
-      </c>
-      <c r="F28" t="inlineStr">
+        <v>0.002024</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2985,288 +3533,349 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shares issued for exploration activities</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash and cash equivalents (Note 5)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>7.496238</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.203597</v>
+        <v>1.87355</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gain on investments</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Restricted cash (Note 5)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>-0.004157</v>
+        <v>0.025</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-0.009520000000000001</v>
+        <v>0.035</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gain on investments measured at fair value</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Prepaid expenses (Note 6)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
-        <v>-0.045771</v>
+        <v>0.411438</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.025666</v>
+        <v>0.159445</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>-0.450821</v>
+          <t>Tax credits recoverable (Note 9)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.593351</v>
+        <v>1.244955</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tax credits recoverable</t>
+          <t>Prepaid financing expense (Note 8)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E33" s="5" t="n">
+        <v>0.399095</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-1.244955</v>
+        <v>0.332578</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-Current Assets</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Investments (Note 7)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>InvestmentsAndAdvances</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.389162</v>
+        <v>0.132988</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.251993</v>
+        <v>0.168174</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-Current Assets</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Prepaid financing expense (Note 8)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>3.249711</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>-2.168118</v>
+        <v>0.332578</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Non-Current Assets</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Restricted cash</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Exploration and evaluation assets (Note 9)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.01</v>
+        <v>3.557734</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.01</v>
+        <v>3.591734</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net cash used in Operating Activities</t>
+          <t>Accounts payable and accrued liabilities (Note 18)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-3.70475</v>
+        <v>2.532332</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-8.318147</v>
+        <v>0.342964</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Issuance of shares and warrants</t>
+          <t>Flow-through share premium liability (Note 10)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>10.562627</v>
+        <v>1.151052</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2.695459</v>
+        <v>0.718477</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Total Liabilities</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-0.5600889999999999</v>
-      </c>
-      <c r="F39" t="inlineStr">
+        <v>3.683384</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1.061441</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3275,24 +3884,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Issuance of shares via exercise of options and</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Capital stock (Note 11)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>0.018132</v>
-      </c>
-      <c r="F40" t="inlineStr">
+        <v>26.342634</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>30.657018</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3301,113 +3917,133 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>warrants</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net cash provided by Financing Activities</t>
+          <t>Contributed surplus (Note 11)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>10.02067</v>
+        <v>4.917414</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>2.695459</v>
+        <v>5.309401</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>warrants</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Net change in cash for the year</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>6.31592</v>
+        <v>-21.947674</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-5.622688</v>
+        <v>-29.575088</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>warrants</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of</t>
+          <t>Total Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1.180318</v>
+        <v>9.312374</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>7.496238</v>
+        <v>6.391331</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>the year</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of the</t>
+          <t>Total Liabilities and Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>7.496238</v>
+        <v>12.995758</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1.87355</v>
+        <v>7.452772</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3418,20 +4054,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>February 28, 2025 February</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>0.002024</v>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>-7.627414</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-23.442719</v>
       </c>
     </row>
     <row r="46">
@@ -3442,20 +4087,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Recognition of flow-through liability</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
-        <v>1.442938</v>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.744846</v>
+        <v>2.496911</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>3.318721</v>
       </c>
     </row>
     <row r="47">
@@ -3466,20 +4120,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation</t>
+          <t>Financing expense</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>0.022825</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.034</v>
+        <v>0.399095</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.332578</v>
       </c>
     </row>
     <row r="48">
@@ -3488,20 +4147,27 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of debt</t>
+          <t>Shares issued for exploration activities</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>0.646918</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.203597</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.252139</v>
       </c>
     </row>
     <row r="49">
@@ -3510,18 +4176,29 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of accounts</t>
+          <t>Shares to be issued for exploration activities</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>0.489876</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.02125</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.100126</v>
       </c>
     </row>
     <row r="50">
@@ -3532,20 +4209,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>payable</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Shares issued upon exercise of restricted</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>0.474648</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>2.14161</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.013477</v>
       </c>
     </row>
     <row r="51">
@@ -3556,12 +4244,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>share units</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Shares issued for finders’ fees</t>
+          <t>Lease interest</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -3570,8 +4258,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.057737</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.000757</v>
       </c>
     </row>
     <row r="52">
@@ -3582,22 +4275,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>share units</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warrants issued for financing fee</t>
+          <t>Interest on financial liability</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.798188</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.000993</v>
       </c>
     </row>
     <row r="53">
@@ -3608,20 +4306,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>share units</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for broker fees</t>
+          <t>Foreign currency translation gain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.418693</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.009520000000000001</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.002146</v>
       </c>
     </row>
     <row r="54">
@@ -3632,12 +4335,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>share units</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Residual value of warrants issued as part of</t>
+          <t>Gain on amortization of flow-through share premium liability</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -3647,7 +4350,10 @@
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.025286</v>
+        <v>-1.177421</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-1.258391</v>
       </c>
     </row>
     <row r="55">
@@ -3658,19 +4364,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Transfer of contributed surplus upon warrant</t>
+          <t>Loss (gain) on investments measured at fair value through profit or loss</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>0.007815000000000001</v>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>-0.025666</v>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3679,752 +4390,936 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mining exploration and metallurgy, net of tax</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mining exploration and metallurgy, net of tax total</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
-        <v>3.520097</v>
+        <v>-0.450821</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>3.9398</v>
+        <v>0.593351</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.101042</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>credits</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 11 and 12)</t>
+          <t>Tax credits/grants receivable</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>1.646973</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>2.496911</v>
+        <v>-1.244955</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-2.055893</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>credits</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Professional fees (Note 12)</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.996483</v>
+        <v>0.389162</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.480361</v>
+        <v>0.251993</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.934148</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>credits</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Business development</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
-        <v>0.8542419999999999</v>
+        <v>3.249711</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.677042</v>
+        <v>-2.168118</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>2.540687</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Research and development expenses</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Research and development expenses total</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Restricted cash</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>0.433799</v>
+        <v>0.01</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.47127</v>
+        <v>-0.01</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.005</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 12)</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0.392729</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.066967</v>
+        <v>-8.318147</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-21.239861</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Management fees (Note 12)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from issuance of shares and warrants</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>2.695459</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>29.366528</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Regulatory and compliance expenses</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>0.184735</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.161112</v>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.1367</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>General administrative expenses</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0.177714</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0.224686</v>
+          <t>Proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>8.516406</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Directors’ fees (Note 12)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>0.0864</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.01</v>
+          <t>Proceeds from exercise of options</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>1.119999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>TotalExpenses</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>-8.599171999999999</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>-8.528149000000001</v>
+          <t>Payment of lease liabilities</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-0.008302</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other Income/(expenses)</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0.057712</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0.136788</v>
+          <t>Proceeds from bridge loan</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.72558</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other Income/(expenses)</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Financing expense (Note 8 and 12)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>-0.066515</v>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.399095</v>
+        <v>2.695459</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>39.583511</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other Income/(expenses)</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Impairment of mineral property (Note 9)</t>
+          <t>Payment on ROU assets</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>-0.109325</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-0.026743</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other Income/(expenses)</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Gain on amortization of flow-through share</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.383218</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>1.177421</v>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.026743</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Foreign currency translation gain (loss)</t>
+          <t>Net increase (decrease) in cash for the year</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>-0.004157</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.009520000000000001</v>
+        <v>-5.622688</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>18.316907</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Unrealized gain on investments (Note 7)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>0.045771</v>
+          <t>Cash and cash equivalents, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.025666</v>
+        <v>7.496238</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>1.87355</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Part XII.6 tax and penalties (Note 10)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of the year</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.049565</v>
+        <v>1.87355</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>20.190457</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>-8.292468</v>
+          <t>Recognition of flow-through share premium liability</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-7.627414</v>
+        <v>0.744846</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.722714</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>premium liability</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Loss per common share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>-1.5e-07</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-1e-07</v>
+          <t>Recognition of right-of-use assets</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.103414</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares total</t>
+          <t>Shares issued for exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>55.236302</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>77.530286</v>
+        <v>0.034</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>outstanding – basic and diluted</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>For the years ended February 28, 2025 and February</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>0.002024</v>
+          <t>Shares issued for settlement of accounts payable</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>0.02125</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Balance, February 28, 2023 48,318,722 16,923,000 2,086,279 68,257</t>
+          <t>Shares issued upon exercise of RSUs</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>5.42233</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-13.655206</v>
+        <v>2.14161</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>2.853865</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Shares issued for private placement 20,493,280 9,943,090 619,537 -</t>
+          <t>Shares issued for finders’ fees</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>10.562627</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.057737</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>1.17769</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability - (1,442,938) - -</t>
+          <t>Warrants issued for finders’ fees</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>-1.442938</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.254061</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Share issuance costs - (978,782) - -</t>
+          <t>Residual value of warrants issued as part of units</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>-0.978782</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.025286</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.189269</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Share based compensation - - 1,646,973 -</t>
+          <t>Transfer of contributed surplus upon warrant exercise</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>1.646973</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.607496</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shares and warrants issued for finders’ fees 412,697 169,793 248,900 -</t>
+          <t>Transfer of contributed surplus upon option exercise</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.418693</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.735301</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Warrants issued for loan commitment</t>
+          <t>1. Nature of Operations</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Warrants issued for loan commitment</t>
+          <t>First Phosphate Corp. (the “Company”) was incorporated in British Columbia on September</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.798188</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.798188</v>
+        <v>0.002006</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>1.8e-05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fees</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of warrants 249,863 94,204 (7,815) (68,257)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
-        <v>0.018132</v>
-      </c>
-      <c r="F85" t="inlineStr">
+        <v>-8.292468</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-7.627414</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4433,24 +5328,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of</t>
+          <t>Non-cash expense</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Share based compensation</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
-        <v>0.022825</v>
-      </c>
-      <c r="F86" t="inlineStr">
+        <v>1.646973</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>2.496911</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4459,26 +5361,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shares issued upon exercise of</t>
+          <t>Non-cash expense</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Shares issued upon exercise of</t>
+          <t>Financing fee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="E87" s="5" t="n">
+        <v>0.066515</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.399095</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4487,24 +5390,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>restricted share units</t>
+          <t>Non-cash expense</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of debt 1,708,900 646,918 - -</t>
+          <t>Gain on amortization of flow-through share</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" s="5" t="n">
-        <v>0.646918</v>
-      </c>
-      <c r="F88" t="inlineStr">
+        <v>-0.383219</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-1.177421</v>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4513,24 +5419,29 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of</t>
+          <t>premium liability</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Shares issued for settlement of</t>
+          <t>Impairment of mineral properties</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="n">
-        <v>0.489876</v>
+        <v>0.109325</v>
       </c>
       <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4539,76 +5450,87 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>accounts payable</t>
+          <t>premium liability</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Net loss for the period - - - -</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>-8.292468</v>
+          <t>Shares issued for exploration activities</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-8.292468</v>
+        <v>0.203597</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>accounts payable</t>
+          <t>premium liability</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Balance, February 29, 2024 73,786,772 26,342,634 4,917,414 -</t>
+          <t>Gain on investments</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" s="5" t="n">
-        <v>9.312374</v>
+        <v>-0.004157</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-21.947674</v>
+        <v>-0.009520000000000001</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>accounts payable</t>
+          <t>premium liability</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Shares issued 7,701,312 2,695,459 - -</t>
+          <t>Gain on investments measured at fair value</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" s="5" t="n">
-        <v>2.695459</v>
-      </c>
-      <c r="F92" t="inlineStr">
+        <v>-0.045771</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.025666</v>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4617,24 +5539,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Shares issued for exploration</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Shares issued for exploration</t>
+          <t>Tax credits recoverable</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>0.203597</v>
-      </c>
-      <c r="F93" t="inlineStr">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-1.244955</v>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4643,24 +5570,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Flow -through share premium</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Flow -through share premium</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Net cash used in Operating Activities</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
-        <v>-0.744846</v>
-      </c>
-      <c r="F94" t="inlineStr">
+        <v>-3.70475</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-8.318147</v>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4669,24 +5603,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Share issuance costs - (57,737) - -</t>
+          <t>Issuance of shares and warrants</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" s="5" t="n">
-        <v>-0.057737</v>
-      </c>
-      <c r="F95" t="inlineStr">
+        <v>10.562627</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>2.695459</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4695,24 +5632,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Share based compensation - - 2,496,911 -</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
-        <v>2.496911</v>
+        <v>-0.5600889999999999</v>
       </c>
       <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4721,26 +5667,29 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Warrants issued for finders' fees - (11,400) 11,400 -</t>
+          <t>Issuance of shares via exercise of options and</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" s="5" t="n">
+        <v>0.018132</v>
       </c>
       <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4749,26 +5698,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Residual value of warrants in units</t>
+          <t>warrants</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Residual value of warrants in units</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
+          <t>Net cash provided by Financing Activities</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>10.02067</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>2.695459</v>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4777,24 +5731,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>exploration and evaluation assets</t>
+          <t>warrants</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Shares issued for finders’ fees 230,948 57,737 - -</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Net change in cash for the year</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
-        <v>0.057737</v>
-      </c>
-      <c r="F99" t="inlineStr">
+        <v>6.31592</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>-5.622688</v>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4803,25 +5764,3990 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>warrants</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, beginning of</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>1.180318</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>7.496238</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>the year</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, end of the</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>7.496238</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>1.87355</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>February 28, 2025 February</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Recognition of flow-through liability</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>1.442938</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.744846</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow information</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Shares issued for exploration and evaluation</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>0.022825</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of debt</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>0.646918</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of accounts</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>0.489876</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>payable</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Shares issued upon exercise of restricted</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0.474648</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>2.14161</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>share units</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Shares issued for finders’ fees</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.057737</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>share units</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Warrants issued for financing fee</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>0.798188</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>share units</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Shares and warrants issued for broker fees</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>0.418693</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>share units</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Residual value of warrants issued as part of</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.025286</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Transfer of contributed surplus upon warrant</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>0.007815000000000001</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>(note 8)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>3.9398</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>16.206984</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Share based compensation (notes 14 and 16)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>2.496911</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>3.318721</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Business development</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.677042</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1.891485</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.547328</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.783397</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.998342</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>General and administrative (note 15)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.234686</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>1.208325</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Regulatory and compliance</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.161112</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.183649</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Depreciation expense</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.013477</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy expense</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TotalExpenses</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>-8.528149000000001</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>-24.60438</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Other income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.136788</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.256504</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Other income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Interest expense on leases (note 11)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-0.000757</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Other income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Financing expense (note 9)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-0.399095</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.332578</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gain on amortization of flow-through share</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>1.177421</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>1.258391</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>premium liability</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Foreign currency translation gain (note 7 and</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.002146</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Flow-through (Part XII.6) tax and penalties</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>-0.049565</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>-0.022045</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Unrealized gain on investments (note 7)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.025666</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>-7.627414</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-23.442719</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Loss per common share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-2.1e-07</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares total</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>55.236302</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>77.530286</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>114.281725</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Balance, February 29, 2024 73,786,772 26,342,634 4,917,414 -</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>9.312374</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>-21.947674</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Shares issued 7,701,312 2,695,459 - -</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>2.695459</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Shares issued for exploration activities 774,389 203,597 - -</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>0.203597</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Flow-through share premium liability - (744,846) - -</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>-0.744846</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (57,737) - -</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>-0.057737</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Share based compensation - - 2,496,911 -</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>2.496911</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Warrants issued for finders' fees - (11,400) 11,400 -</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Residual value of warrants in units issued - (25,286) 25,286 -</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Shares issued for acquisition of exploration and evaluation assets 200,000 34,000 - -</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Shares issued for finders’ fees 230,948 57,737 - -</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0.057737</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Shares issued upon exercise of restricted share units 7,170,796 2,141,610 (2,141,610) -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of accounts payable 83,334 21,250 - -</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>-7.627414</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>-7.627414</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Balance, February 28, 2025 89,947,551 30,657,018 5,309,401 -</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>6.391331</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-29.575088</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Shares issued 57,222,975 29,366,528 - -</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>29.366528</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Shares issued for exploration activities 240,132 252,139 - -</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>0.252139</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Shares to be issued for exploration activities - - - 100,126</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>0.100126</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Flow-through share premium liability - (722,714) - -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>-0.722714</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Residual value of warrants in units issued - (189,269) 189,269 -</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (1,568,451) - -</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>-1.568451</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Shares issued for finders’ fees 2,423,220 1,177,690 - -</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>1.17769</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Warrants issued for finders' fees - - 254,061 -</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>0.254061</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Share based compensation - - 3,318,721 -</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>3.318721</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Warrants exercised 17,021,559 9,123,902 (607,496) -</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>8.516406</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Options exercised 3,750,000 1,855,300 (735,301) -</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>1.119999</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Shares issued upon exercise of restricted share units 6,593,575 2,853,865 (2,853,865) -</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Balance, February 28, 2026 177,199,011 72,806,008 4,874,790 100,126</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>24.763117</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>-53.017807</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>(a)                     (b)         Total</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Balance as at February 29, 2024 3,270,709</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>3.557734</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.287025</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>(a)                     (b)         Total</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Acquisition costs -</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.034</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>(a)                     (b)         Total</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Balance as at February 28, 2025 3,270,709</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>3.591734</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.321025</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>(a)                     (b)         Total</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Balance as of February 28, 2026 3,270,709</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>3.591734</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.321025</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Consulting 80,000</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.15497</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Survey, drilling &amp; geophysics 1,960</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>5.29766</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>5.2957</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Metallurgical testing -</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>0.197384</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.197384</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>TCRR mining tax credits (158,703)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>-1.790214</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>-1.631511</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Expense for the year ended February 28, 2025 (76,743)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>3.9398</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>4.016543</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Consulting -</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>0.442856</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.442856</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Survey, drilling &amp; geophysics -</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>17.109718</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>17.109718</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>TCRR mining tax credits -</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>-1.792479</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>-1.792479</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Government grants received -</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>-0.37208</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>-0.37208</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>(a)                 (b)            Total</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Expense for the year ended February 28, 2026 -</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>16.206984</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>16.206984</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>fully expensed in the year.</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Balance, February 29,</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>0.731673</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Amortization for the year                                      (399,095)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Balance, February 28,</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>0.332578</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Right-of-use assets</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Balance as at February 29,</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Depreciation for the year                                                      (13,477)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Balance as at February 28,</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.002026</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>11.  Lease Liabilities</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>months, from December 1, 2025 to August 31, 2028, with no renewal option. The company occupies the space for free in December 2025, then pays a base monthly rent of $3,460 starting January</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>February 28, 2026 February</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>2.8e-05</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Balance, beginning of year</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Recognized during the year</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.106874</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>InterestExpense</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.000757</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>-0.008302</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>28, 2026 total</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.099329</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Balance, end of year – current</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.038878</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Balance, end of year – non-current</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>0.060451</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>28, 2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Balance, end of year</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.099329</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy, net of tax</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mining exploration and metallurgy, net of tax total</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" s="5" t="n">
+        <v>3.520097</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>3.9398</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>credits</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Share based compensation (Note 11 and 12)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" s="5" t="n">
+        <v>1.646973</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>2.496911</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>credits</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Professional fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>0.996483</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.480361</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>credits</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Business development</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>0.8542419999999999</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>0.677042</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Research and development expenses</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Research and development expenses total</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>0.433799</v>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>0.47127</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>0.392729</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>0.066967</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Management fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Regulatory and compliance expenses</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>0.184735</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>0.161112</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>General administrative expenses</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="n">
+        <v>0.177714</v>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>0.224686</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Directors’ fees (Note 12)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="5" t="n">
+        <v>0.0864</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>TotalExpenses</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n">
+        <v>-8.599171999999999</v>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>-8.528149000000001</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Other Income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n">
+        <v>0.057712</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>0.136788</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Other Income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Financing expense (Note 8 and 12)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" s="5" t="n">
+        <v>-0.066515</v>
+      </c>
+      <c r="F199" s="5" t="n">
+        <v>-0.399095</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Other Income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Impairment of mineral property (Note 9)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" s="5" t="n">
+        <v>-0.109325</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Other Income/(expenses)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Gain on amortization of flow-through share</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>0.383218</v>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>1.177421</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>premium liability</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Foreign currency translation gain (loss)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>-0.004157</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>premium liability</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Unrealized gain on investments (Note 7)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="5" t="n">
+        <v>0.045771</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>0.025666</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>premium liability</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Part XII.6 tax and penalties (Note 10)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>-0.049565</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>premium liability</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>-8.292468</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>-7.627414</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>premium liability</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Loss per common share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>-1.5e-07</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>For the years ended February 28, 2025 and February</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>2.9e-05</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Balance, February 28, 2023 48,318,722 16,923,000 2,086,279 68,257</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>5.42233</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>-13.655206</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Shares issued for private placement 20,493,280 9,943,090 619,537 -</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>10.562627</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Flow-through share premium liability - (1,442,938) - -</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>-1.442938</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (978,782) - -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>-0.978782</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Share based compensation - - 1,646,973 -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>1.646973</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Shares and warrants issued for</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Shares and warrants issued for finders’ fees 412,697 169,793 248,900 -</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>0.418693</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Warrants issued for loan commitment</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Warrants issued for loan commitment</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>0.798188</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.798188</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>fees</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of warrants 249,863 94,204 (7,815) (68,257)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
+        <v>0.018132</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Shares issued for acquisition of</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Shares issued for acquisition of</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>0.022825</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Shares issued upon exercise of</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Shares issued upon exercise of</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>restricted share units</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of debt 1,708,900 646,918 - -</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="5" t="n">
+        <v>0.646918</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Shares issued for settlement of</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>0.489876</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
           <t>accounts payable</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Net loss for the period - - - -</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>-8.292468</v>
+      </c>
+      <c r="F220" s="5" t="n">
+        <v>-8.292468</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>accounts payable</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Balance, February 29, 2024 73,786,772 26,342,634 4,917,414 -</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
+        <v>9.312374</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>-21.947674</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>accounts payable</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Shares issued 7,701,312 2,695,459 - -</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" s="5" t="n">
+        <v>2.695459</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Shares issued for exploration</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Shares issued for exploration</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>0.203597</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Flow -through share premium</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Flow -through share premium</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" s="5" t="n">
+        <v>-0.744846</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>liability</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (57,737) - -</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>-0.057737</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>liability</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Share based compensation - - 2,496,911 -</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" s="5" t="n">
+        <v>2.496911</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>liability</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Warrants issued for finders' fees - (11,400) 11,400 -</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Residual value of warrants in units</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Residual value of warrants in units</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Shares issued for finders’ fees 230,948 57,737 - -</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" s="5" t="n">
+        <v>0.057737</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>accounts payable</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Balance, February 28, 2025 89,947,551 30,657,018 5,309,401 -</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" s="5" t="n">
         <v>6.391331</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F230" s="5" t="n">
         <v>-29.575088</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/PHOS.xlsx
+++ b/output/pdf_financials_xlsx/PHOS.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.433799</v>
+        <v>8.599171999999999</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.47127</v>
+        <v>8.528149000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.596168</v>
+        <v>24.60438</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.433799</v>
+        <v>-8.599171999999999</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.47127</v>
+        <v>-8.528149000000001</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.596168</v>
+        <v>-24.60438</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.057712</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.136788</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.256504</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-8.292468</v>
+        <v>-8.35018</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.627414</v>
+        <v>-7.764202</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-23.442719</v>
+        <v>-23.699223</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-8.292468</v>
+        <v>-8.35018</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.627414</v>
+        <v>-7.764202</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-23.429242</v>
+        <v>-23.685746</v>
       </c>
     </row>
     <row r="30">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>-8.528149000000001</v>
+        <v>8.528149000000001</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-24.60438</v>
+        <v>24.60438</v>
       </c>
     </row>
     <row r="122">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -8716,14 +8716,14 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>-8.599171999999999</v>
+        <v>8.599171999999999</v>
       </c>
       <c r="F197" s="5" t="n">
-        <v>-8.528149000000001</v>
+        <v>8.528149000000001</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">

--- a/output/pdf_financials_xlsx/PHOS.xlsx
+++ b/output/pdf_financials_xlsx/PHOS.xlsx
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.698729</v>
+        <v>0.785129</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.066967</v>
+        <v>0.07696699999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.038878</v>
       </c>
     </row>
     <row r="71">
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.038878</v>
       </c>
     </row>
     <row r="72">
@@ -1644,7 +1644,7 @@
         <v>0.718477</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.221678</v>
+        <v>0.1828</v>
       </c>
     </row>
     <row r="76">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.002441170875217365</v>
+        <v>0.004011167091767971</v>
       </c>
     </row>
     <row r="81">
@@ -3102,7 +3102,11 @@
           <t>Lease liabilities (note 11)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8689,7 +8693,11 @@
           <t>Directors’ fees (Note 12)</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E196" s="5" t="n">
         <v>0.0864</v>
       </c>
